--- a/sales_data.xlsx
+++ b/sales_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\23691A3305\PowerBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13137B8D-A5CA-4C4B-978B-B88FBBDD34BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE338CE9-F69E-462C-87B4-4AC7EFFE5F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30563F55-9986-4486-A0C6-65CF611C9815}"/>
   </bookViews>
@@ -1027,6 +1027,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
